--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>122138915</v>
       </c>
       <c r="B33" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>122377161</v>
       </c>
       <c r="B34" t="n">
-        <v>56584</v>
+        <v>56589</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -3860,11 +3860,6 @@
       <c r="E33" t="n">
         <v>100049</v>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>
@@ -3988,11 +3983,6 @@
       </c>
       <c r="E34" t="n">
         <v>100138</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>122138915</v>
       </c>
       <c r="B33" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3859,6 +3859,11 @@
       </c>
       <c r="E33" t="n">
         <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3969,7 +3974,7 @@
         <v>122377161</v>
       </c>
       <c r="B34" t="n">
-        <v>56589</v>
+        <v>56593</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3983,6 +3988,11 @@
       </c>
       <c r="E34" t="n">
         <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -3842,10 +3842,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122138915</v>
+        <v>122377161</v>
       </c>
       <c r="B33" t="n">
-        <v>57399</v>
+        <v>56593</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3880,27 +3880,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>O Tanneflon, Jmt</t>
+          <t>Tanneflon, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476710</v>
+        <v>476668</v>
       </c>
       <c r="R33" t="n">
-        <v>7007978</v>
+        <v>7008052</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3924,27 +3931,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
+          <t>2018-04-26</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Hördes  från skog nära ridvägen. Har även observerats av ortsbor i området.</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3959,49 +3961,49 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>tim beterams</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>tim beterams</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122377161</v>
+        <v>122138915</v>
       </c>
       <c r="B34" t="n">
-        <v>56593</v>
+        <v>57399</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4009,34 +4011,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tanneflon, Jmt</t>
+          <t>O Tanneflon, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476668</v>
+        <v>476710</v>
       </c>
       <c r="R34" t="n">
-        <v>7008052</v>
+        <v>7007978</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4060,22 +4055,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
+          <t>2025-01-12</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hördes  från skog nära ridvägen. Har även observerats av ortsbor i området.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4090,12 +4090,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>tim beterams</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>tim beterams</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -3845,7 +3845,7 @@
         <v>122377161</v>
       </c>
       <c r="B33" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>122138915</v>
       </c>
       <c r="B34" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -4228,7 +4228,7 @@
         <v>122777024</v>
       </c>
       <c r="B36" t="n">
-        <v>100613</v>
+        <v>100621</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122776138</v>
+        <v>122777024</v>
       </c>
       <c r="B35" t="n">
-        <v>56688</v>
+        <v>100623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,39 +4118,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4196,17 +4188,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Satt i en tall innn den flög iväg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +4213,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122777024</v>
+        <v>122776138</v>
       </c>
       <c r="B36" t="n">
-        <v>100621</v>
+        <v>56688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,31 +4229,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4311,13 +4307,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Satt i en tall innn den flög iväg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122777024</v>
+        <v>122776138</v>
       </c>
       <c r="B35" t="n">
-        <v>100623</v>
+        <v>56688</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,31 +4118,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4188,13 +4196,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Satt i en tall innn den flög iväg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4213,10 +4225,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122776138</v>
+        <v>122777024</v>
       </c>
       <c r="B36" t="n">
-        <v>56688</v>
+        <v>100623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4229,39 +4241,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4307,17 +4311,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Satt i en tall innn den flög iväg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122776138</v>
+        <v>122777024</v>
       </c>
       <c r="B35" t="n">
-        <v>56688</v>
+        <v>100631</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,39 +4118,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4196,17 +4188,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Satt i en tall innn den flög iväg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +4213,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122777024</v>
+        <v>122776138</v>
       </c>
       <c r="B36" t="n">
-        <v>100623</v>
+        <v>56688</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,31 +4229,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4311,13 +4307,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Satt i en tall innn den flög iväg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122777024</v>
+        <v>122776138</v>
       </c>
       <c r="B35" t="n">
-        <v>100631</v>
+        <v>56691</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,31 +4118,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4188,13 +4196,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Satt i en tall innn den flög iväg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4213,10 +4225,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122776138</v>
+        <v>122777024</v>
       </c>
       <c r="B36" t="n">
-        <v>56688</v>
+        <v>100634</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4229,39 +4241,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4307,17 +4311,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Satt i en tall innn den flög iväg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122776138</v>
+        <v>122777024</v>
       </c>
       <c r="B35" t="n">
-        <v>56691</v>
+        <v>100636</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,39 +4118,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4196,17 +4188,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Satt i en tall innn den flög iväg.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +4213,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122777024</v>
+        <v>122776138</v>
       </c>
       <c r="B36" t="n">
-        <v>100634</v>
+        <v>56691</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4241,31 +4229,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4311,13 +4307,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Satt i en tall innn den flög iväg.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -4102,10 +4102,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122777024</v>
+        <v>122776138</v>
       </c>
       <c r="B35" t="n">
-        <v>100636</v>
+        <v>56691</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4118,31 +4118,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4188,13 +4196,17 @@
           <t>2025-02-26</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Satt i en tall innn den flög iväg.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4213,10 +4225,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122776138</v>
+        <v>122777024</v>
       </c>
       <c r="B36" t="n">
-        <v>56691</v>
+        <v>100642</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4229,39 +4241,31 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4307,17 +4311,13 @@
           <t>2025-02-26</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Satt i en tall innn den flög iväg.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4334,6 +4334,131 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123837089</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56920</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100091</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Storspov</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Numenius arquata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>O Tanneflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>476710</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7007978</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ljudbox</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -3976,12 +3976,7 @@
         <v>122138915</v>
       </c>
       <c r="B34" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57861</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117299079</v>
+        <v>122138915</v>
       </c>
       <c r="B2" t="n">
-        <v>100097</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tanne NV, Jmt</t>
+          <t>O Tanneflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476679</v>
+        <v>476710</v>
       </c>
       <c r="R2" t="n">
-        <v>7008015</v>
+        <v>7007978</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +752,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2025-01-12</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hördes  från skog nära ridvägen. Har även observerats av ortsbor i området.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,65 +787,74 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117299072</v>
+        <v>122377159</v>
       </c>
       <c r="B3" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100090</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nötkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nucifraga caryocatactes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tanne NV, Jmt</t>
+          <t>Tanneflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476639</v>
+        <v>476711</v>
       </c>
       <c r="R3" t="n">
-        <v>7008035</v>
+        <v>7008022</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +878,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2019-05-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,65 +908,68 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>tim beterams</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>tim beterams</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117299052</v>
+        <v>123837089</v>
       </c>
       <c r="B4" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100091</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Storspov</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Numenius arquata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tanne NV, Jmt</t>
+          <t>O Tanneflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476721</v>
+        <v>476710</v>
       </c>
       <c r="R4" t="n">
-        <v>7008006</v>
+        <v>7007978</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +993,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2025-04-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ljudbox</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,62 +1028,76 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117299058</v>
+        <v>122377161</v>
       </c>
       <c r="B5" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tanne NV, Jmt</t>
+          <t>Tanneflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476590</v>
+        <v>476668</v>
       </c>
       <c r="R5" t="n">
-        <v>7008074</v>
+        <v>7008052</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1124,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2018-04-26</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,62 +1154,73 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>tim beterams</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>tim beterams</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117299064</v>
+        <v>122776138</v>
       </c>
       <c r="B6" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tanne NV, Jmt</t>
+          <t>O Tannefon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476560</v>
+        <v>476669</v>
       </c>
       <c r="R6" t="n">
-        <v>7008074</v>
+        <v>7008020</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1247,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Satt i en tall innn den flög iväg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,62 +1272,66 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117299057</v>
+        <v>132942979</v>
       </c>
       <c r="B7" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57153</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tanne NV, Jmt</t>
+          <t>Tanneflon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476602</v>
+        <v>476689</v>
       </c>
       <c r="R7" t="n">
-        <v>7008040</v>
+        <v>7008003</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1358,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-25</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>06:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,62 +1388,61 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Albin Enetjärn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117299068</v>
+        <v>117299046</v>
       </c>
       <c r="B8" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476601</v>
+        <v>476604</v>
       </c>
       <c r="R8" t="n">
-        <v>7008058</v>
+        <v>7008040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1371,6 +1483,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1389,37 +1502,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117299055</v>
+        <v>117299073</v>
       </c>
       <c r="B9" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476669</v>
+        <v>476584</v>
       </c>
       <c r="R9" t="n">
-        <v>7008040</v>
+        <v>7008043</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1599,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117299065</v>
+        <v>117299075</v>
       </c>
       <c r="B10" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476587</v>
+        <v>476761</v>
       </c>
       <c r="R10" t="n">
-        <v>7008035</v>
+        <v>7007966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,15 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117299077</v>
+        <v>117299047</v>
       </c>
       <c r="B11" t="n">
-        <v>100097</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1609,21 +1707,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>219847</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476588</v>
+        <v>476561</v>
       </c>
       <c r="R11" t="n">
-        <v>7008075</v>
+        <v>7008081</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,15 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117299075</v>
+        <v>117299048</v>
       </c>
       <c r="B12" t="n">
-        <v>97753</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1711,21 +1804,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1828,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476761</v>
+        <v>476587</v>
       </c>
       <c r="R12" t="n">
-        <v>7007966</v>
+        <v>7008034</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,37 +1890,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117299076</v>
+        <v>117299051</v>
       </c>
       <c r="B13" t="n">
-        <v>100097</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476726</v>
+        <v>476728</v>
       </c>
       <c r="R13" t="n">
-        <v>7007998</v>
+        <v>7008010</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,37 +1987,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117299047</v>
+        <v>117299052</v>
       </c>
       <c r="B14" t="n">
-        <v>97859</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +2022,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476561</v>
+        <v>476721</v>
       </c>
       <c r="R14" t="n">
-        <v>7008081</v>
+        <v>7008006</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,15 +2084,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117299054</v>
+        <v>117299053</v>
       </c>
       <c r="B15" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>476679</v>
+        <v>476702</v>
       </c>
       <c r="R15" t="n">
-        <v>7008047</v>
+        <v>7008032</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,37 +2181,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117299050</v>
+        <v>117299054</v>
       </c>
       <c r="B16" t="n">
-        <v>97857</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>476628</v>
+        <v>476679</v>
       </c>
       <c r="R16" t="n">
-        <v>7008055</v>
+        <v>7008047</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,15 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117299067</v>
+        <v>117299055</v>
       </c>
       <c r="B17" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2245,10 +2313,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>476589</v>
+        <v>476669</v>
       </c>
       <c r="R17" t="n">
-        <v>7008052</v>
+        <v>7008040</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,15 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117299070</v>
+        <v>117299056</v>
       </c>
       <c r="B18" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2347,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>476627</v>
+        <v>476653</v>
       </c>
       <c r="R18" t="n">
-        <v>7008055</v>
+        <v>7008018</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,37 +2472,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117299048</v>
+        <v>117299057</v>
       </c>
       <c r="B19" t="n">
-        <v>97859</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219847</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2507,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>476587</v>
+        <v>476602</v>
       </c>
       <c r="R19" t="n">
-        <v>7008034</v>
+        <v>7008040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,15 +2569,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117299069</v>
+        <v>117299058</v>
       </c>
       <c r="B20" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2551,10 +2604,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>476607</v>
+        <v>476590</v>
       </c>
       <c r="R20" t="n">
-        <v>7008049</v>
+        <v>7008074</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,15 +2666,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117299061</v>
+        <v>117299060</v>
       </c>
       <c r="B21" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2653,7 +2701,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>476579</v>
+        <v>476583</v>
       </c>
       <c r="R21" t="n">
         <v>7008073</v>
@@ -2715,15 +2763,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117299051</v>
+        <v>117299061</v>
       </c>
       <c r="B22" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,10 +2798,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>476728</v>
+        <v>476579</v>
       </c>
       <c r="R22" t="n">
-        <v>7008010</v>
+        <v>7008073</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,37 +2860,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117299078</v>
+        <v>117299063</v>
       </c>
       <c r="B23" t="n">
-        <v>100097</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2895,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>476633</v>
+        <v>476571</v>
       </c>
       <c r="R23" t="n">
-        <v>7008029</v>
+        <v>7008077</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,37 +2957,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117299049</v>
+        <v>117299064</v>
       </c>
       <c r="B24" t="n">
-        <v>97857</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2992,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>476653</v>
+        <v>476560</v>
       </c>
       <c r="R24" t="n">
-        <v>7008018</v>
+        <v>7008074</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,15 +3054,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117299053</v>
+        <v>117299065</v>
       </c>
       <c r="B25" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3061,10 +3089,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>476702</v>
+        <v>476587</v>
       </c>
       <c r="R25" t="n">
-        <v>7008032</v>
+        <v>7008035</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,15 +3151,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117299071</v>
+        <v>117299066</v>
       </c>
       <c r="B26" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3163,10 +3186,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>476633</v>
+        <v>476583</v>
       </c>
       <c r="R26" t="n">
-        <v>7008047</v>
+        <v>7008043</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,15 +3248,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117299060</v>
+        <v>117299067</v>
       </c>
       <c r="B27" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3265,10 +3283,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>476583</v>
+        <v>476589</v>
       </c>
       <c r="R27" t="n">
-        <v>7008073</v>
+        <v>7008052</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,37 +3345,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117299073</v>
+        <v>117299068</v>
       </c>
       <c r="B28" t="n">
-        <v>97753</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3367,10 +3380,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>476584</v>
+        <v>476601</v>
       </c>
       <c r="R28" t="n">
-        <v>7008043</v>
+        <v>7008058</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,15 +3442,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117299066</v>
+        <v>117299069</v>
       </c>
       <c r="B29" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3469,10 +3477,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>476583</v>
+        <v>476607</v>
       </c>
       <c r="R29" t="n">
-        <v>7008043</v>
+        <v>7008049</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,15 +3539,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117299056</v>
+        <v>117299070</v>
       </c>
       <c r="B30" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3571,10 +3574,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>476653</v>
+        <v>476627</v>
       </c>
       <c r="R30" t="n">
-        <v>7008018</v>
+        <v>7008055</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,15 +3636,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117299063</v>
+        <v>117299071</v>
       </c>
       <c r="B31" t="n">
-        <v>97836</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3673,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>476571</v>
+        <v>476633</v>
       </c>
       <c r="R31" t="n">
-        <v>7008077</v>
+        <v>7008047</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,54 +3733,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117299046</v>
+        <v>117299072</v>
       </c>
       <c r="B32" t="n">
-        <v>97753</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219790</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>476604</v>
+        <v>476639</v>
       </c>
       <c r="R32" t="n">
-        <v>7008040</v>
+        <v>7008035</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3823,7 +3812,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3842,15 +3830,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122377161</v>
+        <v>117299049</v>
       </c>
       <c r="B33" t="n">
-        <v>56594</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3858,53 +3841,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>221952</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tanneflon, Jmt</t>
+          <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>476668</v>
+        <v>476653</v>
       </c>
       <c r="R33" t="n">
-        <v>7008052</v>
+        <v>7008018</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3931,22 +3895,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2018-04-26</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3961,72 +3915,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>tim beterams</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>tim beterams</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122138915</v>
+        <v>117299050</v>
       </c>
       <c r="B34" t="n">
-        <v>57881</v>
+        <v>99140</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>221952</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>O Tanneflon, Jmt</t>
+          <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>476710</v>
+        <v>476628</v>
       </c>
       <c r="R34" t="n">
-        <v>7007978</v>
+        <v>7008055</v>
       </c>
       <c r="S34" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4050,27 +3992,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-01-12</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Hördes  från skog nära ridvägen. Har även observerats av ortsbor i området.</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4085,27 +4012,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122776138</v>
+        <v>117299076</v>
       </c>
       <c r="B35" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,50 +4035,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>222498</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>O Tannefon, Jmt</t>
+          <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>476669</v>
+        <v>476726</v>
       </c>
       <c r="R35" t="n">
-        <v>7008020</v>
+        <v>7007998</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4183,17 +4089,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Satt i en tall innn den flög iväg.</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4208,27 +4109,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122777024</v>
+        <v>117299077</v>
       </c>
       <c r="B36" t="n">
-        <v>100642</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4254,24 +4150,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>O Tannefon, Jmt</t>
+          <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>476669</v>
+        <v>476588</v>
       </c>
       <c r="R36" t="n">
-        <v>7008020</v>
+        <v>7008075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4298,12 +4186,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4312,80 +4200,66 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123837089</v>
+        <v>117299078</v>
       </c>
       <c r="B37" t="n">
-        <v>56942</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100091</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Storspov</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Numenius arquata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>O Tanneflon, Jmt</t>
+          <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>476710</v>
+        <v>476633</v>
       </c>
       <c r="R37" t="n">
-        <v>7007978</v>
+        <v>7008029</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4409,27 +4283,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>09:01</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>09:01</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ljudbox</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4444,66 +4303,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132942979</v>
+        <v>117299079</v>
       </c>
       <c r="B38" t="n">
-        <v>57136</v>
+        <v>101326</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>222498</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tanneflon, Jmt</t>
+          <t>Tanne NV, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>476689</v>
+        <v>476679</v>
       </c>
       <c r="R38" t="n">
-        <v>7008003</v>
+        <v>7008015</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4530,22 +4380,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>06:39</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>06:39</t>
+          <t>2024-05-25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4560,15 +4400,218 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Albin Enetjärn</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>117299080</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tanne NV, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>476768</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7007969</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-05-25</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>122777024</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>O Tannefon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>476669</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7008020</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17716-2024 artfynd.xlsx
+++ b/artfynd/A 17716-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AZ40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122138915</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -917,6 +927,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122377159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1037,6 +1052,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123837089</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122377161</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1281,6 +1306,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122776138</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1397,6 +1427,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132942979</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1499,6 +1534,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299046</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1596,6 +1636,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299073</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299075</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1790,6 +1840,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299047</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299048</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299051</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2081,6 +2146,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299052</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2178,6 +2248,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299053</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2275,6 +2350,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299054</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2372,6 +2452,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299055</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,6 +2554,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299056</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2566,6 +2656,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299057</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2663,6 +2758,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299058</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2760,6 +2860,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299060</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2857,6 +2962,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299061</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2954,6 +3064,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299063</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3051,6 +3166,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299064</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3148,6 +3268,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299065</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3245,6 +3370,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299066</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3342,6 +3472,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299067</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3439,6 +3574,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299068</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3536,6 +3676,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299069</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3633,6 +3778,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299070</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3730,6 +3880,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299071</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3827,6 +3982,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299072</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3924,6 +4084,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299049</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4021,6 +4186,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299050</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4118,6 +4288,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299076</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4215,6 +4390,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299077</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4312,6 +4492,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299078</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4409,6 +4594,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299079</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4506,6 +4696,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117299080</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4612,8 +4807,54 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122777024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>